--- a/游戏设计王/捕鱼游戏数学-PartIV-可调参数模型.xlsx
+++ b/游戏设计王/捕鱼游戏数学-PartIV-可调参数模型.xlsx
@@ -277,12 +277,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -984,7 +985,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1054,6 +1055,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1782,7 +1786,7 @@
         <f t="shared" ref="D8:D13" si="0">IF(OR(C8="",C8=0),"",IF(C8&lt;=$C$5,"小鱼","大鱼"))</f>
         <v>小鱼</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="38">
         <f t="shared" ref="E8:E13" si="1">IF(OR(C8="",C8=0),"",$C$4/C8)</f>
         <v>0.45</v>
       </c>
@@ -1810,7 +1814,7 @@
         <f t="shared" si="0"/>
         <v>小鱼</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="38">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -1838,7 +1842,7 @@
         <f t="shared" si="0"/>
         <v>小鱼</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="38">
         <f t="shared" si="1"/>
         <v>0.045</v>
       </c>
@@ -1866,7 +1870,7 @@
         <f t="shared" si="0"/>
         <v>大鱼</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="38">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -1894,7 +1898,7 @@
         <f t="shared" si="0"/>
         <v>大鱼</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="38">
         <f t="shared" si="1"/>
         <v>0.009</v>
       </c>
@@ -1922,7 +1926,7 @@
         <f t="shared" si="0"/>
         <v>大鱼</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="38">
         <f t="shared" si="1"/>
         <v>0.0018</v>
       </c>
@@ -2020,7 +2024,7 @@
       <c r="C17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="39">
         <f>IF($C$4="","",$C$4/2)</f>
         <v>0.45</v>
       </c>
@@ -2047,7 +2051,7 @@
       <c r="C18" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="39">
         <f>IF($C$4="","",$C$4/100)</f>
         <v>0.009</v>
       </c>
